--- a/results/log_pv_cap_fit/log_pv_cap_fit_densities_pdensity_estimates.xlsx
+++ b/results/log_pv_cap_fit/log_pv_cap_fit_densities_pdensity_estimates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,41 +462,11 @@
           <t>densities-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_cap_fit ~ (densities): pdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-inverse_distance-Running PooledOLS:inverse_distance for log_pv_cap_fit ~ (densities): pdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-k_nearest-Running PooledOLS:k_nearest for log_pv_cap_fit ~ (densities): pdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-queen-Running PooledOLS:queen for log_pv_cap_fit ~ (densities): pdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-inverse_distance-Running PanelRE:inverse_distance for log_pv_cap_fit ~ (densities): pdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-k_nearest-Running PanelRE:k_nearest for log_pv_cap_fit ~ (densities): pdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-queen-Running PanelRE:queen for log_pv_cap_fit ~ (densities): pdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pdensity</t>
+          <t>D(Population)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,43 +512,13 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>0.012***</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-0.006***</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-0.006***</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-0.006***</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-0.007***</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>-0.007***</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>-0.007***</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -624,43 +564,13 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>0.136+</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-0.741***</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-0.741***</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-0.741***</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2.217***</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2.217***</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2.217***</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -706,43 +616,13 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>0.003*</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.032***</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.032***</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.032***</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -788,126 +668,96 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>0.160***</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.574***</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.574***</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.574***</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-0.240***</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-0.240***</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.240***</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W_pdensity</t>
+          <t>Spatial term, ρ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.895***</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.750***</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.009***</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>0.644***</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.961***</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.815***</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.717***</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W_log_income</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.345*</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.612***</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.872***</t>
-        </is>
-      </c>
+          <t>Spatial term, λ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.978***</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.914***</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.868***</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_log_hholds</t>
+          <t>W(D(Population))</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.050***</t>
+          <t>0.013</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.005</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.008***</t>
+          <t>-0.009***</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -916,32 +766,26 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W_log_sunny_hours</t>
+          <t>W(Income)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.207***</t>
+          <t>0.345*</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.270***</t>
+          <t>0.612***</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.303***</t>
+          <t>0.872***</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -950,891 +794,320 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W_log_pv_cap_fit</t>
+          <t>W(Households)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.895***</t>
+          <t>-0.050***</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.750***</t>
+          <t>-0.005</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.644***</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.961***</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.815***</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.717***</t>
-        </is>
-      </c>
+          <t>-0.008***</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>W(Sunny hours)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.886</t>
+          <t>-0.207***</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.868</t>
+          <t>-0.270***</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.854</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.886</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.866</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.846</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.021</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.260</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.338</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.255</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.255</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.255</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
+          <t>-0.303***</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aic</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-10105.118</t>
+          <t>0.886</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-9639.077</t>
+          <t>0.868</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-9388.540</t>
+          <t>0.854</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-10086.128</t>
+          <t>0.886</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9562.979</t>
+          <t>0.866</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9224.657</t>
+          <t>0.846</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10089.376</t>
+          <t>0.021</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-9454.027</t>
+          <t>0.260</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9053.476</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1138.880</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1138.880</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1138.880</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2388.978</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2388.978</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2388.978</t>
+          <t>0.338</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>schwarz</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-10054.375</t>
+          <t>-10105.118</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-9588.333</t>
+          <t>-9639.077</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-9337.797</t>
+          <t>-9388.540</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-10057.937</t>
+          <t>-10086.128</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-9534.788</t>
+          <t>-9562.979</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9196.466</t>
+          <t>-9224.657</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-10066.823</t>
+          <t>-10089.376</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-9431.474</t>
+          <t>-9454.027</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-9030.923</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>1167.071</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1167.071</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>1167.071</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2417.169</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2417.169</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2417.169</t>
+          <t>-9053.476</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>llr</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5061.559</t>
+          <t>-10054.375</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4828.538</t>
+          <t>-9588.333</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4703.270</t>
+          <t>-9337.797</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5048.064</t>
+          <t>-10057.937</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4786.490</t>
+          <t>-9534.788</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4617.328</t>
+          <t>-9196.466</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5048.688</t>
+          <t>-10066.823</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4731.013</t>
+          <t>-9431.474</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4530.738</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>-564.440</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-564.440</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>-564.440</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-1189.489</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-1189.489</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-1189.489</t>
+          <t>-9030.923</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>Log-Likelihood</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>5061.559</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4828.538</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4703.270</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>5048.064</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4786.490</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4617.328</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>5048.688</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4731.013</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2076</t>
+          <t>4530.738</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    67.021154   1      0.0
-1  LM Marginal Spatial (LM2)    18.960124   1      0.0
-2             LM Joint (LMJ)  4851.321376   2      0.0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    67.021154   1      0.0
-1  LM Marginal Spatial (LM2)     8.306057   1      0.0
-2             LM Joint (LMJ)  4560.825668   2      0.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df       p-value
-0       LM Marginal RE (LM1)    67.021154   1  0.000000e+00
-1  LM Marginal Spatial (LM2)     7.859128   1  1.887379e-15
-2             LM Joint (LMJ)  4553.600990   2  0.000000e+00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial  166.574646  1     0.0
-1  Hausman Specification Test  -35.352845  4     1.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df p-value
-0      LM Conditional Spatial   41.09901  1     0.0
-1  Hausman Specification Test -35.352845  4     1.0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df p-value
-0      LM Conditional Spatial  27.591641  1     0.0
-1  Hausman Specification Test -35.352845  4     1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           pdensity     0.011637  0.001035  11.239164       0.0
-1         log_income    -0.110929  0.069875  -1.587541   0.11239
-2         log_hholds     0.001043  0.001106   0.943212  0.345572
-3    log_sunny_hours     0.119022   0.03202    3.71717  0.000201
-4         W_pdensity     0.012852  0.013305   0.966003  0.334043
-5       W_log_income      0.34456  0.145526   2.367693  0.017899
-6       W_log_hholds    -0.050091  0.015124  -3.312032  0.000926
-7  W_log_sunny_hours    -0.206525  0.050843  -4.062046  0.000049
-8   W_log_pv_cap_fit      0.89498  0.025363   35.28674       0.0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           pdensity     0.011524  0.001119  10.302573       0.0
-1         log_income    -0.041758  0.071686  -0.582518  0.560217
-2         log_hholds     0.001254  0.001194   1.050221  0.293617
-3    log_sunny_hours     0.108621  0.032702   3.321507  0.000895
-4         W_pdensity     0.000421  0.003853   0.109266  0.912991
-5       W_log_income     0.612245  0.091866   6.664573       0.0
-6       W_log_hholds    -0.004827  0.003561  -1.355606  0.175225
-7  W_log_sunny_hours    -0.270298   0.04341  -6.226599       0.0
-8   W_log_pv_cap_fit     0.749623  0.018569  40.368653       0.0</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           pdensity     0.011514  0.001187   9.701661       0.0
-1         log_income     0.022282  0.072356   0.307956  0.758116
-2         log_hholds     0.001172  0.001257   0.932903   0.35087
-3    log_sunny_hours     0.091836  0.033694   2.725613  0.006418
-4         W_pdensity    -0.008846  0.001748  -5.060622       0.0
-5       W_log_income     0.872246  0.082649  10.553646       0.0
-6       W_log_hholds    -0.007651  0.002063   -3.70918  0.000208
-7  W_log_sunny_hours    -0.302604  0.042143  -7.180399       0.0
-8   W_log_pv_cap_fit     0.644445  0.019799   32.54893       0.0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          var_names coefficients   std_err    zt_stat      prob
-0          pdensity     0.011554  0.001034  11.177727       0.0
-1        log_income    -0.031723  0.028547  -1.111252   0.26646
-2        log_hholds     0.001227  0.001107    1.10808  0.267827
-3   log_sunny_hours      0.04993  0.022471   2.221981  0.026285
-4  W_log_pv_cap_fit     0.961446  0.009953  96.601485       0.0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          var_names coefficients   std_err    zt_stat      prob
-0          pdensity     0.011117   0.00112   9.922581       0.0
-1        log_income     0.309296  0.037297   8.292711       0.0
-2        log_hholds     0.001782    0.0012   1.484762  0.137607
-3   log_sunny_hours     0.007989  0.023531   0.339525  0.734215
-4  W_log_pv_cap_fit     0.815395  0.013918  58.585123       0.0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          var_names coefficients   std_err    zt_stat      prob
-0          pdensity     0.012252  0.001202  10.190517       0.0
-1        log_income     0.507894  0.042117  12.059167       0.0
-2        log_hholds     0.001809  0.001288   1.405056  0.160005
-3   log_sunny_hours    -0.009622  0.025227  -0.381419  0.702892
-4  W_log_pv_cap_fit     0.717418  0.015988  44.870926       0.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err     zt_stat      prob
-0         pdensity       0.0116  0.001033   11.231941       0.0
-1       log_income    -0.094683  0.069736   -1.357737  0.174547
-2       log_hholds     0.001326  0.001103    1.201572  0.229529
-3  log_sunny_hours     0.120546  0.032055    3.760553   0.00017
-4           lambda     0.977501  0.006278  155.704061       0.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err     zt_stat      prob
-0         pdensity     0.010659  0.001067     9.99261       0.0
-1       log_income     0.065804  0.069688    0.944277  0.345028
-2       log_hholds     0.001976  0.001133    1.743422   0.08126
-3  log_sunny_hours     0.142533  0.032871    4.336161  0.000014
-4           lambda     0.913591   0.00834  109.541077       0.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         pdensity     0.012249  0.000971  12.614788       0.0
-1       log_income     0.135767   0.06945   1.954894  0.050596
-2       log_hholds     0.002704  0.001118   2.417748  0.015617
-3  log_sunny_hours     0.159998  0.034169   4.682505  0.000003
-4           lambda     0.867702  0.010921  79.456137       0.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     4.977582  0.501579   9.923822       0.0
-1         pdensity    -0.006396  0.000306 -20.873795       0.0
-2       log_income    -0.740931  0.074908  -9.891168       0.0
-3       log_hholds      0.03195  0.008554    3.73483  0.000193
-4  log_sunny_hours     0.573747  0.152772   3.755573  0.000178</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     4.977582  0.501579   9.923822       0.0
-1         pdensity    -0.006396  0.000306 -20.873795       0.0
-2       log_income    -0.740931  0.074908  -9.891168       0.0
-3       log_hholds      0.03195  0.008554    3.73483  0.000193
-4  log_sunny_hours     0.573747  0.152772   3.755573  0.000178</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     4.977582  0.501579   9.923822       0.0
-1         pdensity    -0.006396  0.000306 -20.873795       0.0
-2       log_income    -0.740931  0.074908  -9.891168       0.0
-3       log_hholds      0.03195  0.008554    3.73483  0.000193
-4  log_sunny_hours     0.573747  0.152772   3.755573  0.000178</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.933411   0.20886 -23.620639       0.0
-1         pdensity    -0.007201  0.000712 -10.108117       0.0
-2       log_income     2.217407  0.044245  50.117055       0.0
-3       log_hholds    -0.000055  0.002268  -0.024396  0.980537
-4  log_sunny_hours    -0.240223  0.044346  -5.416986       0.0</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.933411   0.20886 -23.620639       0.0
-1         pdensity    -0.007201  0.000712 -10.108117       0.0
-2       log_income     2.217407  0.044245  50.117055       0.0
-3       log_hholds    -0.000055  0.002268  -0.024396  0.980537
-4  log_sunny_hours    -0.240223  0.044346  -5.416986       0.0</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.933411   0.20886 -23.620639       0.0
-1         pdensity    -0.007201  0.000712 -10.108117       0.0
-2       log_income     2.217407  0.044245  50.117055       0.0
-3       log_hholds    -0.000055  0.002268  -0.024396  0.980537
-4  log_sunny_hours    -0.240223  0.044346  -5.416986       0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_inverse_distance  \
-pdensity                                     0.233188   
-log_income                                   2.224638   
-log_hholds                                  -0.467039   
-log_sunny_hours                             -0.833209   
-                 direct_ML_LagFE(SLX)_inverse_distance  \
-pdensity                                      0.011637   
-log_income                                   -0.110929   
-log_hholds                                    0.001043   
-log_sunny_hours                               0.119022   
-                 indirect_ML_LagFE(SLX)_inverse_distance  
-pdensity                                        0.221551  
-log_income                                      2.335567  
-log_hholds                                     -0.468082  
-log_sunny_hours                                -0.952231  </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_k_nearest  \
-pdensity                              0.047708   
-log_income                            2.278510   
-log_hholds                           -0.014272   
-log_sunny_hours                      -0.645734   
-                 direct_ML_LagFE(SLX)_k_nearest  \
-pdensity                               0.011524   
-log_income                            -0.041758   
-log_hholds                             0.001254   
-log_sunny_hours                        0.108621   
-                 indirect_ML_LagFE(SLX)_k_nearest  
-pdensity                                 0.036184  
-log_income                               2.320268  
-log_hholds                              -0.015526  
-log_sunny_hours                         -0.754354  </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
-pdensity                          0.007502                    0.011514   
-log_income                        2.515866                    0.022282   
-log_hholds                       -0.018220                    0.001172   
-log_sunny_hours                  -0.592786                    0.091836   
-                 indirect_ML_LagFE(SLX)_queen  
-pdensity                            -0.004011  
-log_income                           2.493584  
-log_hholds                          -0.019393  
-log_sunny_hours                     -0.684622  </t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_inverse_distance  \
-pdensity                                0.299681   
-log_income                             -0.822805   
-log_hholds                              0.031828   
-log_sunny_hours                         1.295058   
-                 direct_ML_LagFE_inverse_distance  \
-pdensity                                 0.011554   
-log_income                              -0.031723   
-log_hholds                               0.001227   
-log_sunny_hours                          0.049930   
-                 indirect_ML_LagFE_inverse_distance  
-pdensity                                   0.288127  
-log_income                                -0.791082  
-log_hholds                                 0.030601  
-log_sunny_hours                            1.245128  </t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
-pdensity                         0.060220                   0.011117   
-log_income                       1.675445                   0.309296   
-log_hholds                       0.009652                   0.001782   
-log_sunny_hours                  0.043277                   0.007989   
-                 indirect_ML_LagFE_k_nearest  
-pdensity                            0.049103  
-log_income                          1.366149  
-log_hholds                          0.007870  
-log_sunny_hours                     0.035288  </t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_queen  direct_ML_LagFE_queen  \
-pdensity                     0.043359               0.012252   
-log_income                   1.797334               0.507894   
-log_hholds                   0.006403               0.001809   
-log_sunny_hours             -0.034051              -0.009622   
-                 indirect_ML_LagFE_queen  
-pdensity                        0.031106  
-log_income                      1.289441  
-log_hholds                      0.004594  
-log_sunny_hours                -0.024429  </t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>lambda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.978***</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.914***</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.868***</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CONSTANT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>4.978***</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>4.978***</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>4.978***</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-4.933***</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-4.933***</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>-4.933***</t>
+          <t>N obs.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2076</t>
         </is>
       </c>
     </row>
